--- a/uploads/Esempio_Appello (C1).xlsx
+++ b/uploads/Esempio_Appello (C1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniudamce-my.sharepoint.com/personal/163002_spes_uniud_it/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alice\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4230EAB4-F8BD-47AA-B2A7-C7821966869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0775E525-567E-4C78-A789-DDCDA6823FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A12E206-6DB9-4C73-9262-66589F64AA7C}"/>
   </bookViews>
@@ -532,7 +532,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -550,6 +550,12 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -572,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -585,6 +591,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -902,7 +909,7 @@
   <dimension ref="A1:R40"/>
   <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="56.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
@@ -912,7 +919,7 @@
     <col min="17" max="17" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -929,7 +936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -937,7 +944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -945,7 +952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -953,7 +960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -967,7 +974,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -975,7 +982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -983,7 +990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -991,8 +998,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1000,7 +1007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1016,7 +1023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1024,7 +1031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1032,15 +1039,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>31</v>

--- a/uploads/Esempio_Appello (C1).xlsx
+++ b/uploads/Esempio_Appello (C1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alice\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniudamce-my.sharepoint.com/personal/163002_spes_uniud_it/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0775E525-567E-4C78-A789-DDCDA6823FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4230EAB4-F8BD-47AA-B2A7-C7821966869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A12E206-6DB9-4C73-9262-66589F64AA7C}"/>
   </bookViews>
@@ -532,7 +532,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -550,12 +550,6 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -578,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -591,7 +585,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -909,7 +902,7 @@
   <dimension ref="A1:R40"/>
   <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
@@ -919,7 +912,7 @@
     <col min="17" max="17" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -936,7 +929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -944,7 +937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -952,7 +945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -960,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -974,7 +967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -982,7 +975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -990,7 +983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -998,8 +991,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1007,7 +1000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1015,7 +1008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1023,7 +1016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1031,7 +1024,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1039,16 +1032,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>31</v>
